--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260926_221534.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260926_221534.xlsx
@@ -6340,7 +6340,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260926_221534.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260926_221534.xlsx
@@ -6340,7 +6340,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
